--- a/practice/answers/q029.xlsx
+++ b/practice/answers/q029.xlsx
@@ -70092,7 +70092,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>(c) No. Brandon holds vastly more acres (about 6.7 million against 0.39 million) despite the lower average yield (59.6 vs 72.1), so yield cannot be what drives the acreage difference -- seed availability, agronomics, familiarity or cost must be doing the work.</t>
